--- a/Sajjad data/by_country_and_state/USA/MO.xlsx
+++ b/Sajjad data/by_country_and_state/USA/MO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="398">
   <si>
     <t>Business Name</t>
   </si>
@@ -1175,6 +1175,36 @@
   </si>
   <si>
     <t>2026-10-25T09:39:27.304Z</t>
+  </si>
+  <si>
+    <t>Plaza Implants</t>
+  </si>
+  <si>
+    <t>(816) 359-8248</t>
+  </si>
+  <si>
+    <t>4546 Main St, Kansas City, MO 64111</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Plaza+Implants/data=!4m7!3m6!1s0x87c0efc0a2f421ef:0xfdd330cff952a6e7!8m2!3d39.0441002!4d-94.5870488!16s%2Fg%2F11gcjvk350!19sChIJ7yH0osDvwIcR56ZS-c8w0_0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:22:13.676Z</t>
+  </si>
+  <si>
+    <t>Dentistry</t>
+  </si>
+  <si>
+    <t>(844) 969-3679</t>
+  </si>
+  <si>
+    <t>6320 Brookside Plaza #131, Kansas City, MO 64113</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentistry/data=!4m7!3m6!1s0x87c0eff2e3be518d:0x261efedc9bee0e75!8m2!3d39.0131863!4d-94.591001!16s%2Fg%2F11p74m59jc!19sChIJjVG-4_LvwIcRdQ7um9z-HiY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:22:27.025Z</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4278,6 +4308,88 @@
         <v>387</v>
       </c>
     </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>388</v>
+      </c>
+      <c r="B67" t="s">
+        <v>389</v>
+      </c>
+      <c r="C67" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" t="s">
+        <v>390</v>
+      </c>
+      <c r="E67" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>37</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>30</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>391</v>
+      </c>
+      <c r="M67" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>393</v>
+      </c>
+      <c r="B68" t="s">
+        <v>394</v>
+      </c>
+      <c r="C68" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" t="s">
+        <v>395</v>
+      </c>
+      <c r="E68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>37</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>221</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>396</v>
+      </c>
+      <c r="M68" t="s">
+        <v>397</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
